--- a/input/ES/alignment_targets_disability.xlsx
+++ b/input/ES/alignment_targets_disability.xlsx
@@ -91,7 +91,7 @@
     <t>Produced</t>
   </si>
   <si>
-    <t>11 Aug 2026</t>
+    <t>26 Sep 2026</t>
   </si>
 </sst>
 </file>
@@ -545,7 +545,7 @@
         <v>2011</v>
       </c>
       <c r="B2" s="14">
-        <v>0.017781062051653862</v>
+        <v>0.017780954018235207</v>
       </c>
     </row>
     <row r="3">
@@ -553,7 +553,7 @@
         <v>2012</v>
       </c>
       <c r="B3" s="15">
-        <v>0.019774775952100754</v>
+        <v>0.019774759188294411</v>
       </c>
     </row>
     <row r="4">
@@ -561,7 +561,7 @@
         <v>2013</v>
       </c>
       <c r="B4" s="16">
-        <v>0.021094854921102524</v>
+        <v>0.021094942465424538</v>
       </c>
     </row>
     <row r="5">
@@ -569,7 +569,7 @@
         <v>2014</v>
       </c>
       <c r="B5" s="17">
-        <v>0.020844141021370888</v>
+        <v>0.020844148471951485</v>
       </c>
     </row>
     <row r="6">
@@ -577,7 +577,7 @@
         <v>2015</v>
       </c>
       <c r="B6" s="18">
-        <v>0.020391145721077919</v>
+        <v>0.020390788093209267</v>
       </c>
     </row>
     <row r="7">
@@ -585,7 +585,7 @@
         <v>2016</v>
       </c>
       <c r="B7" s="19">
-        <v>0.023220615461468697</v>
+        <v>0.023220537230372429</v>
       </c>
     </row>
     <row r="8">
@@ -593,7 +593,7 @@
         <v>2017</v>
       </c>
       <c r="B8" s="20">
-        <v>0.019853942096233368</v>
+        <v>0.019853891804814339</v>
       </c>
     </row>
     <row r="9">
@@ -601,7 +601,7 @@
         <v>2018</v>
       </c>
       <c r="B9" s="21">
-        <v>0.018116153776645661</v>
+        <v>0.018116116523742676</v>
       </c>
     </row>
     <row r="10">
@@ -617,7 +617,7 @@
         <v>2020</v>
       </c>
       <c r="B11" s="23">
-        <v>0.021490041166543961</v>
+        <v>0.021490026265382767</v>
       </c>
     </row>
     <row r="12">
@@ -625,7 +625,7 @@
         <v>2021</v>
       </c>
       <c r="B12" s="24">
-        <v>0.022664805874228477</v>
+        <v>0.022664735093712807</v>
       </c>
     </row>
     <row r="13">
@@ -633,7 +633,7 @@
         <v>2022</v>
       </c>
       <c r="B13" s="25">
-        <v>0.020326118916273117</v>
+        <v>0.020326137542724609</v>
       </c>
     </row>
     <row r="14">
@@ -641,7 +641,7 @@
         <v>2023</v>
       </c>
       <c r="B14" s="26">
-        <v>0.020534282550215721</v>
+        <v>0.02053426206111908</v>
       </c>
     </row>
   </sheetData>
